--- a/verification/cases/roundtrip/legacy_indexed_colors/init.xlsx
+++ b/verification/cases/roundtrip/legacy_indexed_colors/init.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/database/legacy-indexed-colors/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BE9D8B6-BEA6-B249-B92F-0776801557C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A976511-F3C0-4A79-819E-11C101CA731B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7240" yWindow="4340" windowWidth="31480" windowHeight="23080" xr2:uid="{04FD9A7D-7B2C-5C44-8ABA-7E26ACEA7C19}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{04FD9A7D-7B2C-5C44-8ABA-7E26ACEA7C19}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexedColors" sheetId="1" r:id="rId1"/>
     <sheet name="Formulas" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1326,7 +1326,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+  <wetp:taskpane dockstate="right" visibility="1" width="438" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -1349,16 +1349,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8382E100-D92F-0A4C-903E-1533E5559BF1}">
   <dimension ref="B2:F66"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="5.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>0</v>
       </c>
@@ -1389,11 +1389,11 @@
         <v>7</v>
       </c>
       <c r="F3">
-        <f>B3*2</f>
+        <f t="shared" ref="F3:F34" si="0">B3*2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>1</v>
       </c>
@@ -1407,11 +1407,11 @@
         <v>7</v>
       </c>
       <c r="F4">
-        <f>B4*2</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>2</v>
       </c>
@@ -1425,11 +1425,11 @@
         <v>7</v>
       </c>
       <c r="F5">
-        <f>B5*2</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>3</v>
       </c>
@@ -1443,11 +1443,11 @@
         <v>7</v>
       </c>
       <c r="F6">
-        <f>B6*2</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>4</v>
       </c>
@@ -1461,11 +1461,11 @@
         <v>7</v>
       </c>
       <c r="F7">
-        <f>B7*2</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>5</v>
       </c>
@@ -1479,11 +1479,11 @@
         <v>7</v>
       </c>
       <c r="F8">
-        <f>B8*2</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>6</v>
       </c>
@@ -1497,11 +1497,11 @@
         <v>7</v>
       </c>
       <c r="F9">
-        <f>B9*2</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>7</v>
       </c>
@@ -1515,11 +1515,11 @@
         <v>7</v>
       </c>
       <c r="F10">
-        <f>B10*2</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>8</v>
       </c>
@@ -1533,11 +1533,11 @@
         <v>7</v>
       </c>
       <c r="F11">
-        <f>B11*2</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>9</v>
       </c>
@@ -1551,11 +1551,11 @@
         <v>7</v>
       </c>
       <c r="F12">
-        <f>B12*2</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>10</v>
       </c>
@@ -1569,11 +1569,11 @@
         <v>7</v>
       </c>
       <c r="F13">
-        <f>B13*2</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>11</v>
       </c>
@@ -1587,11 +1587,11 @@
         <v>7</v>
       </c>
       <c r="F14">
-        <f>B14*2</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>12</v>
       </c>
@@ -1605,11 +1605,11 @@
         <v>7</v>
       </c>
       <c r="F15">
-        <f>B15*2</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>13</v>
       </c>
@@ -1623,11 +1623,11 @@
         <v>7</v>
       </c>
       <c r="F16">
-        <f>B16*2</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>14</v>
       </c>
@@ -1641,11 +1641,11 @@
         <v>7</v>
       </c>
       <c r="F17">
-        <f>B17*2</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>15</v>
       </c>
@@ -1659,11 +1659,11 @@
         <v>7</v>
       </c>
       <c r="F18">
-        <f>B18*2</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>16</v>
       </c>
@@ -1677,11 +1677,11 @@
         <v>7</v>
       </c>
       <c r="F19">
-        <f>B19*2</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>17</v>
       </c>
@@ -1695,11 +1695,11 @@
         <v>7</v>
       </c>
       <c r="F20">
-        <f>B20*2</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>18</v>
       </c>
@@ -1713,11 +1713,11 @@
         <v>7</v>
       </c>
       <c r="F21">
-        <f>B21*2</f>
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>19</v>
       </c>
@@ -1731,11 +1731,11 @@
         <v>7</v>
       </c>
       <c r="F22">
-        <f>B22*2</f>
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>20</v>
       </c>
@@ -1749,11 +1749,11 @@
         <v>7</v>
       </c>
       <c r="F23">
-        <f>B23*2</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>21</v>
       </c>
@@ -1767,11 +1767,11 @@
         <v>7</v>
       </c>
       <c r="F24">
-        <f>B24*2</f>
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>22</v>
       </c>
@@ -1785,11 +1785,11 @@
         <v>7</v>
       </c>
       <c r="F25">
-        <f>B25*2</f>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>23</v>
       </c>
@@ -1803,11 +1803,11 @@
         <v>7</v>
       </c>
       <c r="F26">
-        <f>B26*2</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>24</v>
       </c>
@@ -1821,11 +1821,11 @@
         <v>7</v>
       </c>
       <c r="F27">
-        <f>B27*2</f>
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>25</v>
       </c>
@@ -1839,11 +1839,11 @@
         <v>7</v>
       </c>
       <c r="F28">
-        <f>B28*2</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>26</v>
       </c>
@@ -1857,11 +1857,11 @@
         <v>7</v>
       </c>
       <c r="F29">
-        <f>B29*2</f>
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>27</v>
       </c>
@@ -1875,11 +1875,11 @@
         <v>7</v>
       </c>
       <c r="F30">
-        <f>B30*2</f>
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>28</v>
       </c>
@@ -1893,11 +1893,11 @@
         <v>7</v>
       </c>
       <c r="F31">
-        <f>B31*2</f>
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>29</v>
       </c>
@@ -1911,11 +1911,11 @@
         <v>7</v>
       </c>
       <c r="F32">
-        <f>B32*2</f>
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>30</v>
       </c>
@@ -1929,11 +1929,11 @@
         <v>7</v>
       </c>
       <c r="F33">
-        <f>B33*2</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>31</v>
       </c>
@@ -1947,11 +1947,11 @@
         <v>7</v>
       </c>
       <c r="F34">
-        <f>B34*2</f>
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>32</v>
       </c>
@@ -1965,11 +1965,11 @@
         <v>7</v>
       </c>
       <c r="F35">
-        <f>B35*2</f>
+        <f t="shared" ref="F35:F66" si="1">B35*2</f>
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>33</v>
       </c>
@@ -1983,11 +1983,11 @@
         <v>7</v>
       </c>
       <c r="F36">
-        <f>B36*2</f>
+        <f t="shared" si="1"/>
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>34</v>
       </c>
@@ -2001,11 +2001,11 @@
         <v>7</v>
       </c>
       <c r="F37">
-        <f>B37*2</f>
+        <f t="shared" si="1"/>
         <v>68</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>35</v>
       </c>
@@ -2019,11 +2019,11 @@
         <v>7</v>
       </c>
       <c r="F38">
-        <f>B38*2</f>
+        <f t="shared" si="1"/>
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>36</v>
       </c>
@@ -2037,11 +2037,11 @@
         <v>7</v>
       </c>
       <c r="F39">
-        <f>B39*2</f>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>37</v>
       </c>
@@ -2055,11 +2055,11 @@
         <v>7</v>
       </c>
       <c r="F40">
-        <f>B40*2</f>
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>38</v>
       </c>
@@ -2073,11 +2073,11 @@
         <v>7</v>
       </c>
       <c r="F41">
-        <f>B41*2</f>
+        <f t="shared" si="1"/>
         <v>76</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>39</v>
       </c>
@@ -2091,11 +2091,11 @@
         <v>7</v>
       </c>
       <c r="F42">
-        <f>B42*2</f>
+        <f t="shared" si="1"/>
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>40</v>
       </c>
@@ -2109,11 +2109,11 @@
         <v>7</v>
       </c>
       <c r="F43">
-        <f>B43*2</f>
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>41</v>
       </c>
@@ -2127,11 +2127,11 @@
         <v>7</v>
       </c>
       <c r="F44">
-        <f>B44*2</f>
+        <f t="shared" si="1"/>
         <v>82</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>42</v>
       </c>
@@ -2145,11 +2145,11 @@
         <v>7</v>
       </c>
       <c r="F45">
-        <f>B45*2</f>
+        <f t="shared" si="1"/>
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>43</v>
       </c>
@@ -2163,11 +2163,11 @@
         <v>7</v>
       </c>
       <c r="F46">
-        <f>B46*2</f>
+        <f t="shared" si="1"/>
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>44</v>
       </c>
@@ -2181,11 +2181,11 @@
         <v>7</v>
       </c>
       <c r="F47">
-        <f>B47*2</f>
+        <f t="shared" si="1"/>
         <v>88</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>45</v>
       </c>
@@ -2199,11 +2199,11 @@
         <v>7</v>
       </c>
       <c r="F48">
-        <f>B48*2</f>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>46</v>
       </c>
@@ -2217,11 +2217,11 @@
         <v>7</v>
       </c>
       <c r="F49">
-        <f>B49*2</f>
+        <f t="shared" si="1"/>
         <v>92</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>47</v>
       </c>
@@ -2235,11 +2235,11 @@
         <v>7</v>
       </c>
       <c r="F50">
-        <f>B50*2</f>
+        <f t="shared" si="1"/>
         <v>94</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>48</v>
       </c>
@@ -2253,11 +2253,11 @@
         <v>7</v>
       </c>
       <c r="F51">
-        <f>B51*2</f>
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>49</v>
       </c>
@@ -2271,11 +2271,11 @@
         <v>7</v>
       </c>
       <c r="F52">
-        <f>B52*2</f>
+        <f t="shared" si="1"/>
         <v>98</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>50</v>
       </c>
@@ -2289,11 +2289,11 @@
         <v>7</v>
       </c>
       <c r="F53">
-        <f>B53*2</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>51</v>
       </c>
@@ -2307,11 +2307,11 @@
         <v>7</v>
       </c>
       <c r="F54">
-        <f>B54*2</f>
+        <f t="shared" si="1"/>
         <v>102</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>52</v>
       </c>
@@ -2325,11 +2325,11 @@
         <v>7</v>
       </c>
       <c r="F55">
-        <f>B55*2</f>
+        <f t="shared" si="1"/>
         <v>104</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>53</v>
       </c>
@@ -2343,11 +2343,11 @@
         <v>7</v>
       </c>
       <c r="F56">
-        <f>B56*2</f>
+        <f t="shared" si="1"/>
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>54</v>
       </c>
@@ -2361,11 +2361,11 @@
         <v>7</v>
       </c>
       <c r="F57">
-        <f>B57*2</f>
+        <f t="shared" si="1"/>
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>55</v>
       </c>
@@ -2379,11 +2379,11 @@
         <v>7</v>
       </c>
       <c r="F58">
-        <f>B58*2</f>
+        <f t="shared" si="1"/>
         <v>110</v>
       </c>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>56</v>
       </c>
@@ -2397,11 +2397,11 @@
         <v>7</v>
       </c>
       <c r="F59">
-        <f>B59*2</f>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>57</v>
       </c>
@@ -2415,11 +2415,11 @@
         <v>7</v>
       </c>
       <c r="F60">
-        <f>B60*2</f>
+        <f t="shared" si="1"/>
         <v>114</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>58</v>
       </c>
@@ -2433,11 +2433,11 @@
         <v>7</v>
       </c>
       <c r="F61">
-        <f>B61*2</f>
+        <f t="shared" si="1"/>
         <v>116</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>59</v>
       </c>
@@ -2451,11 +2451,11 @@
         <v>7</v>
       </c>
       <c r="F62">
-        <f>B62*2</f>
+        <f t="shared" si="1"/>
         <v>118</v>
       </c>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>60</v>
       </c>
@@ -2469,11 +2469,11 @@
         <v>7</v>
       </c>
       <c r="F63">
-        <f>B63*2</f>
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B64">
         <v>61</v>
       </c>
@@ -2487,11 +2487,11 @@
         <v>7</v>
       </c>
       <c r="F64">
-        <f>B64*2</f>
+        <f t="shared" si="1"/>
         <v>122</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>62</v>
       </c>
@@ -2505,11 +2505,11 @@
         <v>7</v>
       </c>
       <c r="F65">
-        <f>B65*2</f>
+        <f t="shared" si="1"/>
         <v>124</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>63</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>7</v>
       </c>
       <c r="F66">
-        <f>B66*2</f>
+        <f t="shared" si="1"/>
         <v>126</v>
       </c>
     </row>
@@ -2535,18 +2535,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{004DBC49-5D2A-844E-BFFE-5EA1937B9A47}">
   <dimension ref="B2:H11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.796875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.296875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>53</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>60</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>Row 1: 10+20</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>61</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>Row 2: 35+15</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>62</v>
       </c>
@@ -2650,7 +2650,7 @@
         <v>Row 3: 100+200</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="94" t="s">
         <v>63</v>
       </c>
@@ -2673,7 +2673,7 @@
       <c r="G7" s="94"/>
       <c r="H7" s="94"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>64</v>
       </c>
@@ -2685,7 +2685,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>65</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>67</v>
       </c>
